--- a/docs/dossiers/dossier-saint-ouen-sur-seine-af87449f.xlsx
+++ b/docs/dossiers/dossier-saint-ouen-sur-seine-af87449f.xlsx
@@ -2249,7 +2249,7 @@
       </c>
       <c r="B7" s="29" t="inlineStr">
         <is>
-          <t>Extraction / vraie restauration possible · Restauration légère possible (sans conduit)</t>
+          <t>Extraction / vraie restauration possible · Restauration légère possible (sans conduit) · Activités restreintes</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-ouen-sur-seine-af87449f.xlsx
+++ b/docs/dossiers/dossier-saint-ouen-sur-seine-af87449f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-ouen-sur-seine-af87449f.xlsx
+++ b/docs/dossiers/dossier-saint-ouen-sur-seine-af87449f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-ouen-sur-seine-af87449f.xlsx
+++ b/docs/dossiers/dossier-saint-ouen-sur-seine-af87449f.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 31/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
